--- a/corpus/xlsx/level-084/template.xlsx
+++ b/corpus/xlsx/level-084/template.xlsx
@@ -39,25 +39,25 @@
   <!-- fixture padding 4 -->
   <definedNames>
     <!-- fixture padding 4 -->
-    <definedName name="ItemRange1">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange2">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange3">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange4">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange5">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange6">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange7">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange8">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange9">'Report'!$A$40:$D$40</definedName>
-    <!-- fixture padding 4 -->
-    <definedName name="ItemRange10">'Report'!$A$40:$D$40</definedName>
+    <definedName name="ItemRange1">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange2">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange3">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange4">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange5">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange6">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange7">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange8">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange9">'Report'!$A$40:$D$41</definedName>
+    <!-- fixture padding 4 -->
+    <definedName name="ItemRange10">'Report'!$A$40:$D$41</definedName>
     <!-- fixture padding 4 -->
   </definedNames>
   <!-- fixture padding 4 -->
@@ -68,7 +68,7 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 4 -->
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <!-- fixture padding 4 -->
   <si>
     <!-- fixture padding 4 -->
@@ -264,6 +264,138 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">l</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">{</t>
       <!-- fixture padding 4 -->
     </r>
@@ -280,6 +412,70 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">c</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">us</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">t</t>
       <!-- fixture padding 4 -->
     </r>
@@ -296,6 +492,614 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">o</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">m</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">r}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">{</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">c</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">o</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">u</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">n</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">{</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">s</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">p</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">c</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">{</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">n</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">b</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">l</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">{</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">l</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">i</t>
       <!-- fixture padding 4 -->
     </r>
@@ -328,10 +1132,478 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">r</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">l}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">N</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">m</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">Q</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">u</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">n</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">y</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">P</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">r</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">c</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">T</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">o</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">t</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">a</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">l</t>
       <!-- fixture padding 4 -->
     </r>
     <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">{</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">d.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">it</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
     <r>
       <!-- fixture padding 4 -->
       <rPr>
@@ -360,23 +1632,87 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">ms</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">[i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">]</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.n</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">am</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e}</t>
       <!-- fixture padding 4 -->
     </r>
     <!-- fixture padding 4 -->
@@ -396,6 +1732,170 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">{d</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">te</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">ms</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">[i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">].</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">qu</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">an</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">ti</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">ty}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">{</t>
       <!-- fixture padding 4 -->
     </r>
@@ -412,6 +1912,154 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
+      <t xml:space="preserve">d.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">it</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">em</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">s[</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">i</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">].</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">pr</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">ic</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">e}</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+  </si>
+  <!-- fixture padding 4 -->
+  <si>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
       <t xml:space="preserve">{</t>
       <!-- fixture padding 4 -->
     </r>
@@ -428,1259 +2076,103 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
-      <t xml:space="preserve">c</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">u</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">st</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">o</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">m</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">r</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">c</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">o</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">u</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">n</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">s</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">p</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">c</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">d</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">n</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">b</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">l</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">d</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">l</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">r</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">l</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">N</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">m</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">Q</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">u</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">n</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">y</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">P</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">r</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">c</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">T</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">o</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">a</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">l</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">#e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">ac</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">h i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">te</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">ms</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}}{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{n</t>
+      <t xml:space="preserve">d.</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">it</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">em</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">s[</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">i+</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">1]</t>
+      <!-- fixture padding 4 -->
+    </r>
+    <!-- fixture padding 4 -->
+    <r>
+      <!-- fixture padding 4 -->
+      <rPr>
+        <!-- fixture padding 4 -->
+        <b/>
+        <!-- fixture padding 4 -->
+        <sz val="11"/>
+        <!-- fixture padding 4 -->
+        <rFont val="Calibri"/>
+        <!-- fixture padding 4 -->
+      </rPr>
+      <!-- fixture padding 4 -->
+      <t xml:space="preserve">.n</t>
       <!-- fixture padding 4 -->
     </r>
     <!-- fixture padding 4 -->
@@ -1712,319 +2204,7 @@
         <!-- fixture padding 4 -->
       </rPr>
       <!-- fixture padding 4 -->
-      <t xml:space="preserve">e}}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">q</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">u</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">an</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">t</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">y</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-  </si>
-  <!-- fixture padding 4 -->
-  <si>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">{</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">p</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">r</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">i</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">c</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">e</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
-      <!-- fixture padding 4 -->
-    </r>
-    <!-- fixture padding 4 -->
-    <r>
-      <!-- fixture padding 4 -->
-      <rPr>
-        <!-- fixture padding 4 -->
-        <b/>
-        <!-- fixture padding 4 -->
-        <sz val="11"/>
-        <!-- fixture padding 4 -->
-        <rFont val="Calibri"/>
-        <!-- fixture padding 4 -->
-      </rPr>
-      <!-- fixture padding 4 -->
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">e}</t>
       <!-- fixture padding 4 -->
     </r>
     <!-- fixture padding 4 -->
@@ -3946,7 +4126,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4008,7 +4188,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4070,7 +4250,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4132,7 +4312,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4194,7 +4374,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4256,7 +4436,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4318,7 +4498,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4380,7 +4560,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4442,7 +4622,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4504,7 +4684,7 @@
       <!-- fixture padding 4 -->
       <xdr:nvPicPr>
         <!-- fixture padding 4 -->
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <!-- fixture padding 4 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 4 -->
@@ -4551,9 +4731,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 4 -->
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
-  <!-- fixture padding 4 -->
-  <autoFilter ref="A39:D40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
+  <!-- fixture padding 4 -->
+  <autoFilter ref="A39:D41"/>
   <!-- fixture padding 4 -->
   <tableColumns count="4">
     <!-- fixture padding 4 -->
@@ -4576,7 +4756,7 @@
 <!-- fixture padding 4 -->
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <!-- fixture padding 4 -->
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <!-- fixture padding 4 -->
   <!-- fixture padding 4 -->
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5231,21 +5411,21 @@
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
-      <c r="E40" s="0" t="inlineStr">
-        <!-- fixture padding 4 -->
-        <is>
-          <!-- fixture padding 4 -->
-          <t xml:space="preserve">{{/each}}</t>
-          <!-- fixture padding 4 -->
-        </is>
-        <!-- fixture padding 4 -->
-      </c>
-      <!-- fixture padding 4 -->
     </row>
     <!-- fixture padding 4 -->
+    <row r="41">
+      <!-- fixture padding 4 -->
+      <c r="A41" s="0" t="s">
+        <!-- fixture padding 4 -->
+        <v>14</v>
+        <!-- fixture padding 4 -->
+      </c>
+      <!-- fixture padding 4 -->
+    </row>
+    <!-- fixture padding 4 -->
   </sheetData>
   <!-- fixture padding 4 -->
-  <autoFilter ref="A39:D40"/>
+  <autoFilter ref="A39:D41"/>
   <!-- fixture padding 4 -->
   <mergeCells count="10">
     <!-- fixture padding 4 -->
@@ -5271,7 +5451,7 @@
     <!-- fixture padding 4 -->
   </mergeCells>
   <!-- fixture padding 4 -->
-  <conditionalFormatting sqref="B40:B40">
+  <conditionalFormatting sqref="B40:B41">
     <!-- fixture padding 4 -->
     <cfRule type="cellIs" priority="1" operator="greaterThan">
       <!-- fixture padding 4 -->
@@ -5283,7 +5463,7 @@
   <!-- fixture padding 4 -->
   <dataValidations count="8">
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5291,7 +5471,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5299,7 +5479,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5307,7 +5487,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5315,7 +5495,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5323,7 +5503,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5331,7 +5511,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5339,7 +5519,7 @@
       <!-- fixture padding 4 -->
     </dataValidation>
     <!-- fixture padding 4 -->
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I41">
       <!-- fixture padding 4 -->
       <formula1>0</formula1>
       <!-- fixture padding 4 -->
@@ -5374,7 +5554,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>22</v>
+        <v>23</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5419,7 +5599,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>23</v>
+        <v>24</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5464,7 +5644,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>24</v>
+        <v>25</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5509,7 +5689,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>14</v>
+        <v>15</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5554,7 +5734,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>15</v>
+        <v>16</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5599,7 +5779,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>16</v>
+        <v>17</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5644,7 +5824,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>17</v>
+        <v>18</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5689,7 +5869,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>18</v>
+        <v>19</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5734,7 +5914,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>19</v>
+        <v>20</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5779,7 +5959,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>20</v>
+        <v>21</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
@@ -5824,7 +6004,7 @@
       <!-- fixture padding 4 -->
       <c r="A1" s="0" t="s">
         <!-- fixture padding 4 -->
-        <v>21</v>
+        <v>22</v>
         <!-- fixture padding 4 -->
       </c>
       <!-- fixture padding 4 -->
